--- a/registration_forms/040_customer_journey_mapping_workshop_registration--registration_forms.xlsx
+++ b/registration_forms/040_customer_journey_mapping_workshop_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -528,7 +528,11 @@
           <t>Workshop Name</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>What is the name of this workshop?</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -543,7 +547,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>attendee_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -553,7 +557,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Enter your name</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -578,10 +582,14 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enter your email address</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -601,10 +609,14 @@
           <t>Phone</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Enter your phone number</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -624,7 +636,11 @@
           <t>Workshop Date</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>What is the date of the workshop?</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -647,7 +663,11 @@
           <t>Workshop Time</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>What is the time of the workshop?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -667,7 +687,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Attendees</t>
+          <t>Will you be attending with any colleagues or team members?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -685,58 +705,58 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>workshop_location</t>
+          <t>workshop_status</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Workshop Location</t>
+          <t>What is the current status of the workshop?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>workshop_notes</t>
+          <t>workshop_manager</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Workshop Notes</t>
+          <t>Who is the primary manager of the workshop?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>workshop_manager</t>
+          <t>workshop_notes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Workshop Manager</t>
+          <t>Are there any additional notes about the workshop?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -754,12 +774,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>workshop_status</t>
+          <t>workshop_manager_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Workshop Status</t>
+          <t>Is this workshop manager available?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -772,17 +792,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>workshop_date</t>
+          <t>workshop_status_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Workshop Date</t>
+          <t>Is this workshop active?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -795,17 +815,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>workshop_time</t>
+          <t>additional_notes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Workshop Time</t>
+          <t>Is there anything else you'd like to share about the workshop?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -818,17 +838,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>workshop_manager</t>
+          <t>future_workshops</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Workshop Manager</t>
+          <t>Will you be attending other workshops in the future?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -841,17 +861,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>workshop_status</t>
+          <t>future_questions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Workshop Status</t>
+          <t>Is there anything else you'd like to share about future workshops?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -864,17 +884,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>workshop_notes</t>
+          <t>other_questions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Workshop Notes</t>
+          <t>Do you have any other questions or concerns about this workshop?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -887,17 +907,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>workshop_manager</t>
+          <t>thank_you</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Workshop Manager</t>
+          <t>Thank you for participating in the workshop registration process!</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -910,17 +930,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>workshop_status</t>
+          <t>end_message</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Workshop Status</t>
+          <t>End Message</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -941,10 +961,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -974,12 +994,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -991,46 +1011,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>workshop_location_choices</t>
+          <t>workshop_status_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>workshop_location_choices</t>
+          <t>workshop_status_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1062,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1059,182 +1079,80 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>workshop_status_choices</t>
+          <t>workshop_manager_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>workshop_status_choices</t>
+          <t>workshop_manager_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>workshop_manager_choices</t>
+          <t>workshop_status_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>workshop_manager_choices</t>
+          <t>workshop_status_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>workshop_status_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>workshop_status_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>workshop_manager_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>workshop_manager_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>workshop_status_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>workshop_status_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Inactive</t>
+          <t>False</t>
         </is>
       </c>
     </row>
